--- a/BVSimulationFiles/94.xlsx
+++ b/BVSimulationFiles/94.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0001739130434782609</v>
+        <v>0.0003478260869565218</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001800772522120759</v>
+        <v>0.0003601545044241518</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001858597031184925</v>
+        <v>0.000371719406236985</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000191274841723707</v>
+        <v>0.000382549683447414</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001963366475959877</v>
+        <v>0.0003926732951919754</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000201058648218123</v>
+        <v>0.000402117296436246</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002054539324663499</v>
+        <v>0.0004109078649326998</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002095351637065722</v>
+        <v>0.0004190703274131444</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002133145925183838</v>
+        <v>0.0004266291850367676</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002168040690571338</v>
+        <v>0.0004336081381142676</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002200150550639915</v>
+        <v>0.000440030110127983</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0002229586355337072</v>
+        <v>0.0004459172710674144</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0002256455300494962</v>
+        <v>0.0004512910600989924</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000228086103794228</v>
+        <v>0.000456172207588456</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0002302903782468499</v>
+        <v>0.0004605807564936998</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002322680415727358</v>
+        <v>0.0004645360831454716</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0002340284587164181</v>
+        <v>0.0004680569174328362</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0002355806812049293</v>
+        <v>0.0004711613624098586</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0002369334566697623</v>
+        <v>0.0004738669133395246</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0002380952380952381</v>
+        <v>0.0004761904761904762</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0001739130434782609</v>
+        <v>0.0003478260869565218</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001800772522120759</v>
+        <v>0.0003601545044241518</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001858597031184925</v>
+        <v>0.000371719406236985</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000191274841723707</v>
+        <v>0.000382549683447414</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001963366475959877</v>
+        <v>0.0003926732951919754</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000201058648218123</v>
+        <v>0.000402117296436246</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0002054539324663499</v>
+        <v>0.0004109078649326998</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002095351637065722</v>
+        <v>0.0004190703274131444</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002133145925183838</v>
+        <v>0.0004266291850367676</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0002168040690571338</v>
+        <v>0.0004336081381142676</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002200150550639915</v>
+        <v>0.000440030110127983</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002229586355337072</v>
+        <v>0.0004459172710674144</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0002256455300494962</v>
+        <v>0.0004512910600989924</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000228086103794228</v>
+        <v>0.000456172207588456</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0002302903782468499</v>
+        <v>0.0004605807564936998</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002322680415727358</v>
+        <v>0.0004645360831454716</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002340284587164181</v>
+        <v>0.0004680569174328362</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002355806812049293</v>
+        <v>0.0004711613624098586</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0002369334566697623</v>
+        <v>0.0004738669133395246</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0002380952380952381</v>
+        <v>0.0004761904761904762</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/94.xlsx
+++ b/BVSimulationFiles/94.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0003478260869565218</v>
+        <v>0.003478260869565218</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003601545044241518</v>
+        <v>0.003601545044241518</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000371719406236985</v>
+        <v>0.00371719406236985</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000382549683447414</v>
+        <v>0.00382549683447414</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0003926732951919754</v>
+        <v>0.003926732951919754</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000402117296436246</v>
+        <v>0.00402117296436246</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0004109078649326998</v>
+        <v>0.004109078649326998</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0004190703274131444</v>
+        <v>0.004190703274131444</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004266291850367676</v>
+        <v>0.004266291850367676</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004336081381142676</v>
+        <v>0.004336081381142676</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000440030110127983</v>
+        <v>0.004400301101279831</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0004459172710674144</v>
+        <v>0.004459172710674144</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004512910600989924</v>
+        <v>0.004512910600989924</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000456172207588456</v>
+        <v>0.00456172207588456</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0004605807564936998</v>
+        <v>0.004605807564936998</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0004645360831454716</v>
+        <v>0.004645360831454716</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0004680569174328362</v>
+        <v>0.004680569174328362</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004711613624098586</v>
+        <v>0.004711613624098586</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0004738669133395246</v>
+        <v>0.004738669133395246</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0004761904761904762</v>
+        <v>0.004761904761904762</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0003478260869565218</v>
+        <v>0.003478260869565218</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0003601545044241518</v>
+        <v>0.003601545044241518</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000371719406236985</v>
+        <v>0.00371719406236985</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000382549683447414</v>
+        <v>0.00382549683447414</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0003926732951919754</v>
+        <v>0.003926732951919754</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000402117296436246</v>
+        <v>0.00402117296436246</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004109078649326998</v>
+        <v>0.004109078649326998</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004190703274131444</v>
+        <v>0.004190703274131444</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004266291850367676</v>
+        <v>0.004266291850367676</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004336081381142676</v>
+        <v>0.004336081381142676</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000440030110127983</v>
+        <v>0.004400301101279831</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004459172710674144</v>
+        <v>0.004459172710674144</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0004512910600989924</v>
+        <v>0.004512910600989924</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000456172207588456</v>
+        <v>0.00456172207588456</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004605807564936998</v>
+        <v>0.004605807564936998</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0004645360831454716</v>
+        <v>0.004645360831454716</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004680569174328362</v>
+        <v>0.004680569174328362</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004711613624098586</v>
+        <v>0.004711613624098586</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004738669133395246</v>
+        <v>0.004738669133395246</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0004761904761904762</v>
+        <v>0.004761904761904762</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/94.xlsx
+++ b/BVSimulationFiles/94.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,61 +421,43 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.02478684210526316</v>
+        <v>0.01623965517241379</v>
       </c>
       <c r="D1" t="n">
-        <v>0.04957368421052632</v>
+        <v>0.03247931034482758</v>
       </c>
       <c r="E1" t="n">
-        <v>0.07436052631578947</v>
+        <v>0.04871896551724138</v>
       </c>
       <c r="F1" t="n">
-        <v>0.09914736842105264</v>
+        <v>0.06495862068965516</v>
       </c>
       <c r="G1" t="n">
-        <v>0.1239342105263158</v>
+        <v>0.08119827586206896</v>
       </c>
       <c r="H1" t="n">
-        <v>0.1487210526315789</v>
+        <v>0.09743793103448276</v>
       </c>
       <c r="I1" t="n">
-        <v>0.1735078947368421</v>
+        <v>0.1136775862068966</v>
       </c>
       <c r="J1" t="n">
-        <v>0.1982947368421053</v>
+        <v>0.1299172413793103</v>
       </c>
       <c r="K1" t="n">
-        <v>0.2230815789473684</v>
+        <v>0.1461568965517241</v>
       </c>
       <c r="L1" t="n">
-        <v>0.2478684210526316</v>
+        <v>0.1623965517241379</v>
       </c>
       <c r="M1" t="n">
-        <v>0.2726552631578947</v>
+        <v>0.1786362068965517</v>
       </c>
       <c r="N1" t="n">
-        <v>0.2974421052631579</v>
+        <v>0.1948758620689655</v>
       </c>
       <c r="O1" t="n">
-        <v>0.3222289473684211</v>
-      </c>
-      <c r="P1" t="n">
-        <v>0.3470157894736842</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>0.3718026315789473</v>
-      </c>
-      <c r="R1" t="n">
-        <v>0.3965894736842105</v>
-      </c>
-      <c r="S1" t="n">
-        <v>0.4213763157894737</v>
-      </c>
-      <c r="T1" t="n">
-        <v>0.4461631578947369</v>
-      </c>
-      <c r="U1" t="n">
-        <v>0.47095</v>
+        <v>0.2111155172413793</v>
       </c>
     </row>
     <row r="2">
@@ -483,64 +465,46 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.003478260869565218</v>
+        <v>0.02097265091808333</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003601545044241518</v>
+        <v>0.02212219357106414</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00371719406236985</v>
+        <v>0.02318236977294947</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00382549683447414</v>
+        <v>0.02415755344824359</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003926732951919754</v>
+        <v>0.02505193509034112</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00402117296436246</v>
+        <v>0.02586952887453188</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004109078649326998</v>
+        <v>0.02661417950797561</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004190703274131444</v>
+        <v>0.0272895688260676</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004266291850367676</v>
+        <v>0.02789922214428669</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004336081381142676</v>
+        <v>0.02844651437429825</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004400301101279831</v>
+        <v>0.02893467591277763</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004459172710674144</v>
+        <v>0.02936679831112268</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004512910600989924</v>
+        <v>0.02974583973393685</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00456172207588456</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.004605807564936998</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.004645360831454716</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.004680569174328362</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.004711613624098586</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.004738669133395246</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.004761904761904762</v>
+        <v>0.03007463021388801</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +512,46 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.003478260869565218</v>
+        <v>0.02097265091808333</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003601545044241518</v>
+        <v>0.02212219357106414</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00371719406236985</v>
+        <v>0.02318236977294947</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00382549683447414</v>
+        <v>0.02415755344824359</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003926732951919754</v>
+        <v>0.02505193509034112</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00402117296436246</v>
+        <v>0.02586952887453188</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004109078649326998</v>
+        <v>0.02661417950797561</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004190703274131444</v>
+        <v>0.0272895688260676</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004266291850367676</v>
+        <v>0.02789922214428669</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004336081381142676</v>
+        <v>0.02844651437429825</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004400301101279831</v>
+        <v>0.02893467591277763</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004459172710674144</v>
+        <v>0.02936679831112268</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004512910600989924</v>
+        <v>0.02974583973393685</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00456172207588456</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.004605807564936998</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.004645360831454716</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.004680569174328362</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.004711613624098586</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.004738669133395246</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.004761904761904762</v>
+        <v>0.03007463021388801</v>
       </c>
     </row>
   </sheetData>
